--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Scan Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,7 +27,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -45,17 +44,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2937"/>
-        <bgColor rgb="001F2937"/>
+        <fgColor rgb="FF1F2937"/>
+        <bgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -76,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -87,9 +101,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -452,19 +472,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="5" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="28.05" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
@@ -517,7 +535,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 18:35:26 UTC</t>
+          <t> </t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1954,6 +1972,1485 @@
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edx.org</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:47:14 UTC</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.udemy.com</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:47:51 UTC</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="90" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.khanacademy.org</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:49:04 UTC</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="108" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.duolingo.com</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:51:15 UTC</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>[CRITICAL] /.env.production
+[CRITICAL] /.env
+[CRITICAL] /adminer.php
+[HIGH] /backup.zip
+[MEDIUM] /elmah.axd
+[MEDIUM] /swagger-ui.html</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.duolingo.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:55:06 UTC</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:55:50 UTC</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:56:54 UTC</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Arbitrary origin reflected with credentials flag enabled
+[HIGH] Origin check bypass using lookalike origin 'https://www.reuters.com.evil-attacker-test.com'
+[HIGH] Origin check bypass using lookalike origin 'https://evil-www.reuters.com'
+[HIGH] Explicitly accepting 'null' origin in CORS policy
+[MEDIUM] Dynamic origin reflection without specifying Vary: Origin</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nationalgeographic.com</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:10:23 UTC</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="72" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:10:48 UTC</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:11:56 UTC</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Arbitrary origin reflected with credentials flag enabled
+[HIGH] Origin check bypass using lookalike origin 'https://www.etsy.com.evil-attacker-test.com'
+[HIGH] Origin check bypass using lookalike origin 'https://evil-www.etsy.com'
+[HIGH] Explicitly accepting 'null' origin in CORS policy
+[MEDIUM] Dynamic origin reflection without specifying Vary: Origin</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:12:36 UTC</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.walmart.com</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:13:29 UTC</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.target.com</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:14:40 UTC</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:16:07 UTC</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="72" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.booking.com</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:29:07 UTC</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.expedia.com</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:30:02 UTC</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="72" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tripadvisor.com</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:31:00 UTC</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Arbitrary origin reflected with credentials flag enabled
+[HIGH] Origin check bypass using lookalike origin 'https://www.tripadvisor.com.evil-attacker-test.com'
+[MEDIUM] Dynamic origin reflection without specifying Vary: Origin</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.airbnb.com</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:32:17 UTC</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="54" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.trip.com</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:33:18 UTC</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cloudflare.com</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:33:55 UTC</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cloudflare.com</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:34:38 UTC</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.heroku.com</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:35:20 UTC</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="54" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digitalocean.com</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:35:51 UTC</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Strict-Transport-Security
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="54" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:36:36 UTC</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.paypal.com</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 14:37:14 UTC</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>[CRITICAL] /.env.production</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:09:51 UTC</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:10:45 UTC</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] /backup.zip
+[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.quora.com</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:11:38 UTC</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Strict-Transport-Security</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pinterest.com</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:12:53 UTC</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>[CRITICAL] /.env.production</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twitch.tv</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:14:40 UTC</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] /backup.zip</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="54" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:15:48 UTC</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="36" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.netflix.com</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:19:40 UTC</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="90" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.disney.com</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:20:53 UTC</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.espn.com</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:21:51 UTC</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.uefa.com</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:24:53 UTC</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:27:01 UTC</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:29:34 UTC</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Strict-Transport-Security</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="90" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.monster.com</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 16:31:42 UTC</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Arbitrary origin reflected with credentials flag enabled
+[HIGH] Origin check bypass using lookalike origin 'https://www.monster.com.evil-attacker-test.com'
+[HIGH] Origin check bypass using lookalike origin 'https://evil-www.monster.com'
+[MEDIUM] Dynamic origin reflection without specifying Vary: Origin</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:50:07 UTC</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Content-Type-Options</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.forbes.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:50:10 UTC</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
         </is>
       </c>
     </row>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3454,6 +3454,43 @@
         </is>
       </c>
     </row>
+    <row r="82" ht="54" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ikea.com</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:27:23 UTC</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3491,6 +3491,2529 @@
         </is>
       </c>
     </row>
+    <row r="83" ht="54" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:42:17 UTC</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="90" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:43:18 UTC</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.apple.com</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:43:58 UTC</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.apple.com</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:50:33 UTC</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="54" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.samsung.com</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:51:03 UTC</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="90" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sony.com</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:51:21 UTC</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="90" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lg.com</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:51:51 UTC</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lenovo.com</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:52:19 UTC</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.lenovo.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.asus.com</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:52:59 UTC</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.acer.com</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:53:50 UTC</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="54" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:54:18 UTC</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.amd.com</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:54:52 UTC</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="54" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.qualcomm.com</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:55:22 UTC</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>[CRITICAL] /.env
+[CRITICAL] /.env.production
+[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="90" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sap.com</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:55:45 UTC</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.sap.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="24" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.salesforce.com</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:56:12 UTC</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="24" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.intuit.com</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:56:29 UTC</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.autodesk.com</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:56:47 UTC</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="54" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:57:12 UTC</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="54" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.costco.com</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:59:14 UTC</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="90" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.homedepot.com</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:59:45 UTC</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="72" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.macys.com</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:00:40 UTC</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.macys.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="72" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nike.com</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:02:21 UTC</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="54" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.puma.com</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:03:17 UTC</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="54" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.uniqlo.com</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:04:36 UTC</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="90" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hm.com</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:04:52 UTC</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="72" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.zara.com</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:05:10 UTC</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="54" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.levi.com</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:05:27 UTC</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="90" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.underarmour.com</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:06:27 UTC</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="24" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lululemon.com</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:07:32 UTC</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="24" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ubereats.com</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:08:08 UTC</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="24" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.doordash.com</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:08:29 UTC</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.grubhub.com</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:09:04 UTC</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="24" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kroger.com</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:15:37 UTC</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="24" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wholefoodsmarket.com</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:17:55 UTC</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="24" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dominos.com</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:18:20 UTC</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="24" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pizzahut.com</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:19:05 UTC</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="90" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kfc.com</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:19:32 UTC</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="24" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mcdonalds.com</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:20:36 UTC</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.starbucks.com</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:21:14 UTC</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.subway.com</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:21:45 UTC</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="36" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coca-cola.com</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:22:07 UTC</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.coca-cola.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="72" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pepsi.com</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:22:26 UTC</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nestle.com</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:22:50 UTC</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="90" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.unilever.com</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:23:21 UTC</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="24" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pg.com</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:24:05 UTC</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="90" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jnj.com</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:24:30 UTC</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="24" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pfizer.com</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:24:54 UTC</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="36" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.roche.com</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:26:04 UTC</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: X-Content-Type-Options</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="36" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.novartis.com</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:26:55 UTC</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="24" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gsk.com</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:27:46 UTC</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="24" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.merck.com</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:28:05 UTC</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="90" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bayer.com</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:28:42 UTC</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sanofi.com</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:29:03 UTC</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.who.int</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:29:30 UTC</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="72" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:30:05 UTC</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="24" customHeight="1">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nih.gov</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:30:48 UTC</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="72" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.webmd.com</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:32:03 UTC</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="72" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.healthline.com</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:32:32 UTC</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="90" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mayoclinic.org</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:33:17 UTC</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>[MEDIUM] Arbitrary origin reflected in Access-Control-Allow-Origin
+[HIGH] Origin check bypass using lookalike origin 'https://www.mayoclinic.org.evil-attacker-test.com'
+[HIGH] Origin check bypass using lookalike origin 'https://evil-www.mayoclinic.org'
+[MEDIUM] Explicitly accepting 'null' origin in CORS policy
+[MEDIUM] Dynamic origin reflection without specifying Vary: Origin</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="36" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.clevelandclinic.org</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Hospital</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:34:16 UTC</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="90" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.harvard.edu</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 14:35:09 UTC</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="36" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mit.edu</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:48:55 UTC</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="24" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.stanford.edu</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:50:41 UTC</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="54" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.berkeley.edu</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:51:19 UTC</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Content-Type-Options</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="54" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.princeton.edu</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:51:47 UTC</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="36" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.yale.edu</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:52:18 UTC</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="24" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cornell.edu</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:52:42 UTC</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="24" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cornell.edu</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:53:06 UTC</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="24" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ox.ac.uk</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:53:26 UTC</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6014,6 +6014,700 @@
         </is>
       </c>
     </row>
+    <row r="152" ht="24" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cam.ac.uk</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:09:55 UTC</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="72" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.codecademy.com</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:10:55 UTC</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="24" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.freecodecamp.org</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12:01 UTC</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="54" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.w3schools.com</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:12:22 UTC</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="24" customHeight="1">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Technology &amp; SaaS</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:13:28 UTC</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="24" customHeight="1">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.geeksforgeeks.org</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:14:24 UTC</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="24" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>https://leetcode.com</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:15:05 UTC</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnn.com</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>News &amp; Media</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:18:35 UTC</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="72" customHeight="1">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cbsnews.com</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>News &amp; Media</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:19:17 UTC</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="90" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>https://abcnews.go.com</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>News &amp; Media</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:20:25 UTC</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-abcnews.go.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="24" customHeight="1">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.washingtonpost.com</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>News &amp; Media</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:21:23 UTC</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="90" customHeight="1">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wsj.com</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>News &amp; Media</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:21:44 UTC</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Arbitrary origin reflected with credentials flag enabled
+[HIGH] Origin check bypass using lookalike origin 'https://www.wsj.com.evil-attacker-test.com'
+[HIGH] Origin check bypass using lookalike origin 'https://evil-www.wsj.com'
+[HIGH] Explicitly accepting 'null' origin in CORS policy
+[MEDIUM] Dynamic origin reflection without specifying Vary: Origin</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="54" customHeight="1">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>News &amp; Media</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:22:09 UTC</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="36" customHeight="1">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aljazeera.com</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>News &amp; Media</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:22:38 UTC</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="72" customHeight="1">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hyatt.com</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>Travel &amp; Hospitality</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:27:01 UTC</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="24" customHeight="1">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hilton.com</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Travel &amp; Hospitality</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:27:29 UTC</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="36" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ihg.com</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:27:57 UTC</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.ihg.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="24" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.accor.com</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:28:23 UTC</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="54" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.airtel.in</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:29:09 UTC</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6708,6 +6708,397 @@
         </is>
       </c>
     </row>
+    <row r="171" ht="24" customHeight="1">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.myvi.in</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:41:49 UTC</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="36" customHeight="1">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tatacommunications.com</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:42:27 UTC</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: X-Content-Type-Options</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="24" customHeight="1">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>https://www.verizon.com</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:42:49 UTC</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="24" customHeight="1">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.att.com</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:43:38 UTC</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.att.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="24" customHeight="1">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>https://www.vodafone.com</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:44:04 UTC</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="24" customHeight="1">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.telekom.com</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:44:23 UTC</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="36" customHeight="1">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>https://www.paypal.com</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:45:08 UTC</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>[CRITICAL] /.env.production</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="24" customHeight="1">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>https://www.visa.com</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:45:28 UTC</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="72" customHeight="1">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mastercard.com</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:45:45 UTC</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="36" customHeight="1">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>https://www.americanexpress.com</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:46:56 UTC</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="24" customHeight="1">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>https://www.stripe.com</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:47:38 UTC</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7099,6 +7099,77 @@
         </is>
       </c>
     </row>
+    <row r="182" ht="36" customHeight="1">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.phonepe.com</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:52:38 UTC</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="24" customHeight="1">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>https://paytm.com</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Banking &amp; Finance</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:53:16 UTC</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7170,6 +7170,184 @@
         </is>
       </c>
     </row>
+    <row r="184" ht="24" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pwc.com</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:54:15 UTC</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="24" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ey.com</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:55:03 UTC</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>[LOW] Access-Control-Allow-Origin is set to '*'</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="24" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kpmg.com</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:55:40 UTC</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="72" customHeight="1">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bain.com</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:56:07 UTC</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="24" customHeight="1">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mckinsey.com</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:57:01 UTC</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7348,6 +7348,259 @@
         </is>
       </c>
     </row>
+    <row r="189" ht="24" customHeight="1">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:57:54 UTC</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="54" customHeight="1">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tcs.com</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:58:13 UTC</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="72" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infosys.com</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:58:37 UTC</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="72" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infosys.com</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:58:59 UTC</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="24" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wipro.com</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:59:25 UTC</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="24" customHeight="1">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hcltech.com</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:59:48 UTC</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="24" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>Corporate</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:00:17 UTC</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] /.well-known/security.txt</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7601,6 +7601,116 @@
         </is>
       </c>
     </row>
+    <row r="196" ht="36" customHeight="1">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>https://www.uber.com</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>Travel &amp; Hospitality</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:01:39 UTC</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="90" customHeight="1">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ola.com</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:02:08 UTC</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: Strict-Transport-Security
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options
+Missing: Referrer-Policy</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="24" customHeight="1">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>https://www.irctc.co.in</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:03:30 UTC</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shieldscope_scan_report.xlsx
+++ b/shieldscope_scan_report.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7711,6 +7711,113 @@
         </is>
       </c>
     </row>
+    <row r="199" ht="54" customHeight="1">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>https://www.emirates.com</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>Travel &amp; Hospitality</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:05:56 UTC</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>Missing: Content-Security-Policy
+Missing: X-Frame-Options
+Missing: X-Content-Type-Options</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t>[INFO] No CORS misconfiguration detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="24" customHeight="1">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>https://www.qatarairways.com</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>Travel &amp; Hospitality</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:06:40 UTC</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>[HIGH] Origin check bypass using lookalike origin 'https://evil-www.qatarairways.com'</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="24" customHeight="1">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>https://www.airindia.com</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>Travel &amp; Hospitality</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-11 14:07:27 UTC</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>None (All Secure)</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>None (Secure)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
